--- a/Dataset/2_label/OPENING_OPENING_V2_10 divisions_per_second.xlsx
+++ b/Dataset/2_label/OPENING_OPENING_V2_10 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1674,6 +1674,114 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>15600</v>
+      </c>
+      <c r="C70" t="n">
+        <v>45</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>15800</v>
+      </c>
+      <c r="C71" t="n">
+        <v>45</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C72" t="n">
+        <v>45</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>16200</v>
+      </c>
+      <c r="C73" t="n">
+        <v>45</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>16400</v>
+      </c>
+      <c r="C74" t="n">
+        <v>45</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>16600</v>
+      </c>
+      <c r="C75" t="n">
+        <v>45</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
